--- a/结果/策略一_连板断板_交易明细.xlsx
+++ b/结果/策略一_连板断板_交易明细.xlsx
@@ -65,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -491,9 +492,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>002636.XSHE</t>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>002636</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +502,7 @@
           <t>2026-01-27</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>25.45543</v>
       </c>
       <c r="E2" t="inlineStr">
@@ -509,13 +510,13 @@
           <t>2026-01-28</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>26.06054350635829</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <v>2.267816181397574</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="5" t="n">
         <v>404.0976524090327</v>
       </c>
     </row>
@@ -525,9 +526,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>000751.XSHE</t>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>000751</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -535,7 +536,7 @@
           <t>2026-01-28</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>6.316309999999999</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -543,13 +544,13 @@
           <t>2026-01-29</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>7.481897222194442</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="4" t="n">
         <v>18.34112773216498</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="5" t="n">
         <v>3591.295703684481</v>
       </c>
     </row>
@@ -559,9 +560,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>002440.XSHE</t>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>002440</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -569,7 +570,7 @@
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>12.36235</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -577,13 +578,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>12.06406841149805</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="6" t="n">
         <v>-2.514148902852708</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="7" t="n">
         <v>-497.2926190268987</v>
       </c>
     </row>
@@ -593,9 +594,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>601388.XSHG</t>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>601388</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -603,7 +604,7 @@
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>4.13413</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -611,13 +612,13 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>4.002679649465569</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>-3.280409464361112</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <v>-650.9586805871619</v>
       </c>
     </row>
@@ -627,9 +628,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>002931.XSHE</t>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>002931</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -637,7 +638,7 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>99.52943</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -645,13 +646,13 @@
           <t>2026-02-04</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>105.0151960924242</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="4" t="n">
         <v>5.406655145233956</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="5" t="n">
         <v>1076.242609623406</v>
       </c>
     </row>
@@ -661,9 +662,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>002491.XSHE</t>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>002491</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -671,7 +672,7 @@
           <t>2026-02-04</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>9.389379999999999</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -679,13 +680,13 @@
           <t>2026-02-05</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>9.001791327966425</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <v>-4.228558053596103</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="7" t="n">
         <v>-833.7743067627578</v>
       </c>
     </row>
@@ -695,9 +696,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>603629.XSHG</t>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>603629</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -705,7 +706,7 @@
           <t>2026-02-04</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>30.09006</v>
       </c>
       <c r="E8" t="inlineStr">
@@ -713,13 +714,13 @@
           <t>2026-02-05</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="3" t="n">
         <v>29.45693659695959</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="6" t="n">
         <v>-2.210411039298421</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="7" t="n">
         <v>-399.0684047829111</v>
       </c>
     </row>
@@ -729,9 +730,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>603618.XSHG</t>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>603618</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -739,7 +740,7 @@
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>12.47246</v>
       </c>
       <c r="E9" t="inlineStr">
@@ -747,13 +748,13 @@
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>14.87270346559388</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="4" t="n">
         <v>19.13242184963054</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="5" t="n">
         <v>3818.053859562288</v>
       </c>
     </row>
@@ -763,9 +764,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>603618.XSHG</t>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>603618</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -773,7 +774,7 @@
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="3" t="n">
         <v>14.29428</v>
       </c>
       <c r="E10" t="inlineStr">
@@ -781,13 +782,13 @@
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="3" t="n">
         <v>15.19258126706813</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="4" t="n">
         <v>6.17532187790939</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="5" t="n">
         <v>1147.533140168514</v>
       </c>
     </row>
@@ -797,9 +798,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>600397.XSHG</t>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>600397</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -807,7 +808,7 @@
           <t>2026-02-24</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="3" t="n">
         <v>16.19618</v>
       </c>
       <c r="E11" t="inlineStr">
@@ -815,13 +816,13 @@
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="3" t="n">
         <v>17.62442210652824</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="4" t="n">
         <v>8.71043885731439</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="5" t="n">
         <v>1692.910027344698</v>
       </c>
     </row>
@@ -831,9 +832,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>603466.XSHG</t>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>603466</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -841,7 +842,7 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="3" t="n">
         <v>12.96295</v>
       </c>
       <c r="E12" t="inlineStr">
@@ -849,13 +850,13 @@
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="3" t="n">
         <v>11.97661246313373</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="6" t="n">
         <v>-7.708445264304248</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="7" t="n">
         <v>-1498.862858083691</v>
       </c>
     </row>
@@ -865,9 +866,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>001896.XSHE</t>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>001896</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -875,7 +876,7 @@
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="3" t="n">
         <v>13.90389</v>
       </c>
       <c r="E13" t="inlineStr">
@@ -883,13 +884,13 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="3" t="n">
         <v>14.20165787158862</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="4" t="n">
         <v>2.037150250981911</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="5" t="n">
         <v>396.5403820437484</v>
       </c>
     </row>
@@ -899,9 +900,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>600722.XSHG</t>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>600722</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -909,7 +910,7 @@
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="3" t="n">
         <v>11.1111</v>
       </c>
       <c r="E14" t="inlineStr">
@@ -917,13 +918,13 @@
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="3" t="n">
         <v>12.58195260124211</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="4" t="n">
         <v>13.12893537867468</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="5" t="n">
         <v>2625.78444994786</v>
       </c>
     </row>
@@ -933,9 +934,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>600590.XSHG</t>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>600590</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -943,7 +944,7 @@
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="3" t="n">
         <v>16.86685</v>
       </c>
       <c r="E15" t="inlineStr">
@@ -951,13 +952,13 @@
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="3" t="n">
         <v>16.29543171765452</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="6" t="n">
         <v>-3.491988901972757</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="7" t="n">
         <v>-647.8873831236311</v>
       </c>
     </row>
@@ -967,9 +968,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>600108.XSHG</t>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>600108</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -977,7 +978,7 @@
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="3" t="n">
         <v>6.816809999999999</v>
       </c>
       <c r="E16" t="inlineStr">
@@ -985,13 +986,13 @@
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="3" t="n">
         <v>6.384947073611835</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G16" s="6" t="n">
         <v>-6.434618147752012</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="7" t="n">
         <v>-1272.043510737544</v>
       </c>
     </row>
@@ -1001,9 +1002,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>600722.XSHG</t>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>600722</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1011,7 +1012,7 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="3" t="n">
         <v>17.36735</v>
       </c>
       <c r="E17" t="inlineStr">
@@ -1019,13 +1020,13 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="3" t="n">
         <v>17.85467547707764</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="4" t="n">
         <v>2.700210509913269</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="5" t="n">
         <v>515.8505109927644</v>
       </c>
     </row>
@@ -1035,9 +1036,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>000539.XSHE</t>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>000539</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1045,7 +1046,7 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="3" t="n">
         <v>6.106099999999999</v>
       </c>
       <c r="E18" t="inlineStr">
@@ -1053,13 +1054,13 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" s="3" t="n">
         <v>6.433688189381398</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="4" t="n">
         <v>5.259018807500921</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="5" t="n">
         <v>1027.587031695404</v>
       </c>
     </row>
@@ -1069,9 +1070,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>600758.XSHG</t>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>600758</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1079,7 +1080,7 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="3" t="n">
         <v>5.53553</v>
       </c>
       <c r="E19" t="inlineStr">
@@ -1087,13 +1088,13 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F19" s="3" t="n">
         <v>5.043219389157406</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G19" s="6" t="n">
         <v>-8.9912941635009</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="7" t="n">
         <v>-1791.776828911829</v>
       </c>
     </row>
@@ -1103,9 +1104,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>603306.XSHG</t>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>603306</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1113,7 +1114,7 @@
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="3" t="n">
         <v>101.0009</v>
       </c>
       <c r="E20" t="inlineStr">
@@ -1121,13 +1122,13 @@
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F20" s="3" t="n">
         <v>100.8107463769468</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="G20" s="6" t="n">
         <v>-0.3391822376883764</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="7" t="n">
         <v>-34.25771127053994</v>
       </c>
     </row>
@@ -1137,9 +1138,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>603698.XSHG</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>603698</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,7 +1148,7 @@
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="3" t="n">
         <v>42.83279</v>
       </c>
       <c r="E21" t="inlineStr">
@@ -1155,13 +1156,13 @@
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F21" s="3" t="n">
         <v>45.96397233078695</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="4" t="n">
         <v>7.196151306039719</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="5" t="n">
         <v>1232.9249507993</v>
       </c>
     </row>
@@ -1171,9 +1172,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>603268.XSHG</t>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>603268</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1181,7 +1182,7 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="3" t="n">
         <v>141.11097</v>
       </c>
       <c r="E22" t="inlineStr">
@@ -1189,13 +1190,13 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F22" s="3" t="n">
         <v>141.6220005690788</v>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" s="4" t="n">
         <v>0.2390971014433146</v>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="H22" s="5" t="n">
         <v>33.73922390885453</v>
       </c>
     </row>
@@ -1205,9 +1206,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>603318.XSHG</t>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>603318</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1215,7 +1216,7 @@
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="3" t="n">
         <v>14.69468</v>
       </c>
       <c r="E23" t="inlineStr">
@@ -1223,13 +1224,13 @@
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" s="3" t="n">
         <v>14.24350024896758</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="G23" s="6" t="n">
         <v>-3.173142869744013</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" s="7" t="n">
         <v>-606.1681478472093</v>
       </c>
     </row>
@@ -1239,9 +1240,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>002081.XSHE</t>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>002081</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1249,7 +1250,7 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="3" t="n">
         <v>6.82682</v>
       </c>
       <c r="E24" t="inlineStr">
@@ -1257,13 +1258,13 @@
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F24" s="3" t="n">
         <v>7.464648057436774</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" s="4" t="n">
         <v>9.235698947173248</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="5" t="n">
         <v>1828.463174309697</v>
       </c>
     </row>
@@ -1273,9 +1274,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>002208.XSHE</t>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>002208</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1283,7 +1284,7 @@
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="3" t="n">
         <v>22.86284</v>
       </c>
       <c r="E25" t="inlineStr">
@@ -1291,13 +1292,13 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="3" t="n">
         <v>24.52334124455271</v>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="G25" s="4" t="n">
         <v>7.152504728712591</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="5" t="n">
         <v>1308.212569694395</v>
       </c>
     </row>
@@ -1307,9 +1308,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>002940.XSHE</t>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>002940</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1317,7 +1318,7 @@
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="3" t="n">
         <v>41.73168999999999</v>
       </c>
       <c r="E26" t="inlineStr">
@@ -1325,13 +1326,13 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F26" s="3" t="n">
         <v>41.41498689650665</v>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="G26" s="6" t="n">
         <v>-0.8704226062029971</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="7" t="n">
         <v>-145.2968254842222</v>
       </c>
     </row>
@@ -1341,9 +1342,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>603663.XSHG</t>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>603663</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1351,7 +1352,7 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" s="3" t="n">
         <v>41.98194</v>
       </c>
       <c r="E27" t="inlineStr">
@@ -1359,13 +1360,13 @@
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="F27" s="3" t="n">
         <v>44.40086439192864</v>
       </c>
-      <c r="G27" s="3" t="n">
+      <c r="G27" s="4" t="n">
         <v>5.647333428823837</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="5" t="n">
         <v>948.3440526755062</v>
       </c>
     </row>
@@ -1375,9 +1376,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>603936.XSHG</t>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>603936</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1385,7 +1386,7 @@
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" s="3" t="n">
         <v>25.93591</v>
       </c>
       <c r="E28" t="inlineStr">
@@ -1393,13 +1394,13 @@
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F28" s="3" t="n">
         <v>24.44658391880607</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="G28" s="6" t="n">
         <v>-5.846484323774392</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" s="7" t="n">
         <v>-1061.437238664764</v>
       </c>
     </row>
@@ -1409,9 +1410,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>002552.XSHE</t>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>002552</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1419,7 +1420,7 @@
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D29" s="3" t="n">
         <v>48.83879</v>
       </c>
       <c r="E29" t="inlineStr">
@@ -1427,13 +1428,13 @@
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F29" s="3" t="n">
         <v>57.81560789560886</v>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" s="4" t="n">
         <v>18.26794551560777</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="H29" s="5" t="n">
         <v>3568.737419072838</v>
       </c>
     </row>
@@ -1443,9 +1444,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>002585.XSHE</t>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>002585</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1453,7 +1454,7 @@
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D30" s="3" t="n">
         <v>10.43042</v>
       </c>
       <c r="E30" t="inlineStr">
@@ -1461,13 +1462,13 @@
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F30" s="3" t="n">
         <v>10.7593897627977</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="4" t="n">
         <v>3.049877300472425</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H30" s="5" t="n">
         <v>604.4185226554781</v>
       </c>
     </row>
@@ -1477,9 +1478,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>002957.XSHE</t>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>002957</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1487,7 +1488,7 @@
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" s="3" t="n">
         <v>55.86581</v>
       </c>
       <c r="E31" t="inlineStr">
@@ -1495,13 +1496,13 @@
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F31" s="3" t="n">
         <v>62.59818456069471</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" s="4" t="n">
         <v>11.93316179454918</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" s="5" t="n">
         <v>1999.96724854063</v>
       </c>
     </row>
@@ -1511,9 +1512,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>002608.XSHE</t>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>002608</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1521,7 +1522,7 @@
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="3" t="n">
         <v>9.81981</v>
       </c>
       <c r="E32" t="inlineStr">
@@ -1529,13 +1530,13 @@
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F32" s="3" t="n">
         <v>10.35527469555386</v>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="G32" s="4" t="n">
         <v>5.34720434875142</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" s="5" t="n">
         <v>1050.170614718254</v>
       </c>
     </row>
@@ -1545,9 +1546,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>000700.XSHE</t>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>000700</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1555,7 +1556,7 @@
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D33" s="3" t="n">
         <v>18.04803</v>
       </c>
       <c r="E33" t="inlineStr">
@@ -1563,13 +1564,13 @@
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="F33" s="3" t="n">
         <v>16.36231211128958</v>
       </c>
-      <c r="G33" s="5" t="n">
+      <c r="G33" s="6" t="n">
         <v>-9.437783831687376</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="H33" s="7" t="n">
         <v>-1873.667463005896</v>
       </c>
     </row>
@@ -1579,9 +1580,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>603859.XSHG</t>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>603859</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1589,7 +1590,7 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D34" s="3" t="n">
         <v>52.36231</v>
       </c>
       <c r="E34" t="inlineStr">
@@ -1597,13 +1598,13 @@
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F34" s="3" t="n">
         <v>52.47414286166162</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="4" t="n">
         <v>0.0978071677297065</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="H34" s="5" t="n">
         <v>15.36422771065467</v>
       </c>
     </row>
@@ -1613,9 +1614,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>001696.XSHE</t>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>001696</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1623,7 +1624,7 @@
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D35" s="3" t="n">
         <v>18.83882</v>
       </c>
       <c r="E35" t="inlineStr">
@@ -1631,13 +1632,13 @@
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="F35" s="3" t="n">
         <v>22.4592301725163</v>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="G35" s="4" t="n">
         <v>19.10293519938252</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="H35" s="5" t="n">
         <v>3598.767576928315</v>
       </c>
     </row>
@@ -1647,9 +1648,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>603186.XSHG</t>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>603186</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1657,7 +1658,7 @@
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D36" s="3" t="n">
         <v>166.17601</v>
       </c>
       <c r="E36" t="inlineStr">
@@ -1665,13 +1666,13 @@
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F36" s="3" t="n">
         <v>178.5024184008831</v>
       </c>
-      <c r="G36" s="3" t="n">
+      <c r="G36" s="4" t="n">
         <v>7.301722076128043</v>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="H36" s="5" t="n">
         <v>1213.371040739874</v>
       </c>
     </row>
@@ -1681,9 +1682,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>605006.XSHG</t>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>605006</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1691,7 +1692,7 @@
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D37" s="3" t="n">
         <v>21.6216</v>
       </c>
       <c r="E37" t="inlineStr">
@@ -1699,13 +1700,13 @@
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="F37" s="3" t="n">
         <v>21.358831076573</v>
       </c>
-      <c r="G37" s="5" t="n">
+      <c r="G37" s="6" t="n">
         <v>-1.318076619617254</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="H37" s="7" t="n">
         <v>-256.4903289484478</v>
       </c>
     </row>
@@ -1715,9 +1716,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>001696.XSHE</t>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>001696</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1725,7 +1726,7 @@
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D38" s="3" t="n">
         <v>22.6226</v>
       </c>
       <c r="E38" t="inlineStr">
@@ -1733,13 +1734,13 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="F38" s="3" t="n">
         <v>23.66431612202809</v>
       </c>
-      <c r="G38" s="3" t="n">
+      <c r="G38" s="4" t="n">
         <v>4.495155706266556</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="H38" s="5" t="n">
         <v>813.5368758446863</v>
       </c>
     </row>
@@ -1749,9 +1750,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>000510.XSHE</t>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>000510</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1759,7 +1760,7 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D39" s="3" t="n">
         <v>22.73271</v>
       </c>
       <c r="E39" t="inlineStr">
@@ -1767,13 +1768,13 @@
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="F39" s="3" t="n">
         <v>21.87238127115236</v>
       </c>
-      <c r="G39" s="5" t="n">
+      <c r="G39" s="6" t="n">
         <v>-3.889597722382977</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="H39" s="7" t="n">
         <v>-707.3687763167418</v>
       </c>
     </row>
@@ -1783,9 +1784,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>601696.XSHG</t>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>601696</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1793,7 +1794,7 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="D40" s="3" t="n">
         <v>13.34333</v>
       </c>
       <c r="E40" t="inlineStr">
@@ -1801,13 +1802,13 @@
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="F40" s="3" t="n">
         <v>12.80253903795968</v>
       </c>
-      <c r="G40" s="5" t="n">
+      <c r="G40" s="6" t="n">
         <v>-4.156357876126371</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="H40" s="7" t="n">
         <v>-776.435166349546</v>
       </c>
     </row>
@@ -1817,9 +1818,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>002515.XSHE</t>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>002515</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1827,7 +1828,7 @@
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="D41" s="3" t="n">
         <v>9.019009999999998</v>
       </c>
       <c r="E41" t="inlineStr">
@@ -1835,13 +1836,13 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="F41" s="3" t="n">
         <v>9.87086725823864</v>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G41" s="4" t="n">
         <v>9.337914818716085</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H41" s="5" t="n">
         <v>1852.812436841268</v>
       </c>
     </row>
@@ -1851,9 +1852,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>603757.XSHG</t>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>603757</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1861,7 +1862,7 @@
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="3" t="n">
         <v>72.69261999999999</v>
       </c>
       <c r="E42" t="inlineStr">
@@ -1869,13 +1870,13 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F42" s="3" t="n">
         <v>73.62069702162917</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="4" t="n">
         <v>1.155280329623761</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="H42" s="5" t="n">
         <v>167.9607079896295</v>
       </c>
     </row>
@@ -1885,9 +1886,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>002990.XSHE</t>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>002990</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1895,7 +1896,7 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D43" s="3" t="n">
         <v>75.20512999999998</v>
       </c>
       <c r="E43" t="inlineStr">
@@ -1903,13 +1904,13 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="F43" s="3" t="n">
         <v>78.27874416317651</v>
       </c>
-      <c r="G43" s="3" t="n">
+      <c r="G43" s="4" t="n">
         <v>3.966404888008725</v>
       </c>
-      <c r="H43" s="4" t="n">
+      <c r="H43" s="5" t="n">
         <v>596.587990470663</v>
       </c>
     </row>
@@ -1919,9 +1920,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>603989.XSHG</t>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>603989</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1929,7 +1930,7 @@
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="D44" s="3" t="n">
         <v>55.83577999999999</v>
       </c>
       <c r="E44" t="inlineStr">
@@ -1937,13 +1938,13 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="F44" s="3" t="n">
         <v>51.28934635295191</v>
       </c>
-      <c r="G44" s="5" t="n">
+      <c r="G44" s="6" t="n">
         <v>-8.250055618138443</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="H44" s="7" t="n">
         <v>-1381.944871446426</v>
       </c>
     </row>
@@ -1953,9 +1954,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>688432.XSHG</t>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>688432</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1963,7 +1964,7 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D45" s="3" t="n">
         <v>39.039</v>
       </c>
       <c r="E45" t="inlineStr">
@@ -1971,13 +1972,13 @@
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="F45" s="3" t="n">
         <v>45.10945823051271</v>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="G45" s="4" t="n">
         <v>15.43856660471619</v>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="H45" s="5" t="n">
         <v>3013.531008407575</v>
       </c>
     </row>
@@ -1987,9 +1988,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>002379.XSHE</t>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>002379</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1997,7 +1998,7 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D46" s="3" t="n">
         <v>18.20819</v>
       </c>
       <c r="E46" t="inlineStr">
@@ -2005,13 +2006,13 @@
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="F46" s="3" t="n">
         <v>18.24844822905671</v>
       </c>
-      <c r="G46" s="3" t="n">
+      <c r="G46" s="4" t="n">
         <v>0.1140664643761551</v>
       </c>
-      <c r="H46" s="4" t="n">
+      <c r="H46" s="5" t="n">
         <v>20.76943855989265</v>
       </c>
     </row>
@@ -2021,9 +2022,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>000603.XSHE</t>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>000603</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2031,7 +2032,7 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D47" s="3" t="n">
         <v>25.16514</v>
       </c>
       <c r="E47" t="inlineStr">
@@ -2039,13 +2040,13 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="F47" s="3" t="n">
         <v>24.06566174408029</v>
       </c>
-      <c r="G47" s="5" t="n">
+      <c r="G47" s="6" t="n">
         <v>-4.475592462807288</v>
       </c>
-      <c r="H47" s="6" t="n">
+      <c r="H47" s="7" t="n">
         <v>-788.4023763664313</v>
       </c>
     </row>
@@ -2055,9 +2056,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>002498.XSHE</t>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>002498</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2065,7 +2066,7 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" s="3" t="n">
         <v>6.766759999999999</v>
       </c>
       <c r="E48" t="inlineStr">
@@ -2073,13 +2074,13 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="F48" s="3" t="n">
         <v>6.750016126065463</v>
       </c>
-      <c r="G48" s="5" t="n">
+      <c r="G48" s="6" t="n">
         <v>-0.3502758428095253</v>
       </c>
-      <c r="H48" s="6" t="n">
+      <c r="H48" s="7" t="n">
         <v>-68.7367443006037</v>
       </c>
     </row>
@@ -2089,9 +2090,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>000533.XSHE</t>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>000533</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2099,7 +2100,7 @@
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D49" s="3" t="n">
         <v>11.53152</v>
       </c>
       <c r="E49" t="inlineStr">
@@ -2107,13 +2108,13 @@
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="F49" s="3" t="n">
         <v>10.44325383170268</v>
       </c>
-      <c r="G49" s="5" t="n">
+      <c r="G49" s="6" t="n">
         <v>-9.53551566395983</v>
       </c>
-      <c r="H49" s="6" t="n">
+      <c r="H49" s="7" t="n">
         <v>-1869.302823017522</v>
       </c>
     </row>
@@ -2123,9 +2124,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>002827.XSHE</t>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>002827</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2133,7 +2134,7 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D50" s="3" t="n">
         <v>48.91886999999999</v>
       </c>
       <c r="E50" t="inlineStr">
@@ -2141,13 +2142,13 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="F50" s="3" t="n">
         <v>52.92715607877307</v>
       </c>
-      <c r="G50" s="3" t="n">
+      <c r="G50" s="4" t="n">
         <v>8.086458334938881</v>
       </c>
-      <c r="H50" s="4" t="n">
+      <c r="H50" s="5" t="n">
         <v>1582.321616189166</v>
       </c>
     </row>
@@ -2157,9 +2158,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>000811.XSHE</t>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>000811</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2167,7 +2168,7 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D51" s="3" t="n">
         <v>40.52047999999999</v>
       </c>
       <c r="E51" t="inlineStr">
@@ -2175,13 +2176,13 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="F51" s="3" t="n">
         <v>42.05650868983274</v>
       </c>
-      <c r="G51" s="3" t="n">
+      <c r="G51" s="4" t="n">
         <v>3.675116053908857</v>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="H51" s="5" t="n">
         <v>595.669866240371</v>
       </c>
     </row>
@@ -2191,9 +2192,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>002080.XSHE</t>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>002080</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2201,7 +2202,7 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n">
+      <c r="D52" s="3" t="n">
         <v>52.1521</v>
       </c>
       <c r="E52" t="inlineStr">
@@ -2209,13 +2210,13 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="F52" s="3" t="n">
         <v>56.62085117789147</v>
       </c>
-      <c r="G52" s="3" t="n">
+      <c r="G52" s="4" t="n">
         <v>8.44840320803462</v>
       </c>
-      <c r="H52" s="4" t="n">
+      <c r="H52" s="5" t="n">
         <v>1321.805906837227</v>
       </c>
     </row>
@@ -2225,9 +2226,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>002579.XSHE</t>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>002579</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2235,7 +2236,7 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D53" s="3" t="n">
         <v>13.7137</v>
       </c>
       <c r="E53" t="inlineStr">
@@ -2243,13 +2244,13 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="F53" s="3" t="n">
         <v>14.74224760634502</v>
       </c>
-      <c r="G53" s="3" t="n">
+      <c r="G53" s="4" t="n">
         <v>7.39223598243314</v>
       </c>
-      <c r="H53" s="4" t="n">
+      <c r="H53" s="5" t="n">
         <v>1419.248692292107</v>
       </c>
     </row>
@@ -2259,9 +2260,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>601208.XSHG</t>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2269,7 +2270,7 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="D54" s="3" t="n">
         <v>42.35231</v>
       </c>
       <c r="E54" t="inlineStr">
@@ -2277,13 +2278,13 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F54" s="2" t="n">
+      <c r="F54" s="3" t="n">
         <v>44.78732617265101</v>
       </c>
-      <c r="G54" s="3" t="n">
+      <c r="G54" s="4" t="n">
         <v>5.635468556975901</v>
       </c>
-      <c r="H54" s="4" t="n">
+      <c r="H54" s="5" t="n">
         <v>954.700445281184</v>
       </c>
     </row>
@@ -2293,9 +2294,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>603186.XSHG</t>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>603186</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2303,7 +2304,7 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D55" s="3" t="n">
         <v>132.4323</v>
       </c>
       <c r="E55" t="inlineStr">
@@ -2311,13 +2312,13 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="F55" s="3" t="n">
         <v>147.1119004484169</v>
       </c>
-      <c r="G55" s="3" t="n">
+      <c r="G55" s="4" t="n">
         <v>10.95144391223909</v>
       </c>
-      <c r="H55" s="4" t="n">
+      <c r="H55" s="5" t="n">
         <v>1450.32490561882</v>
       </c>
     </row>
@@ -2327,9 +2328,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>002437.XSHE</t>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>002437</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2337,7 +2338,7 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="D56" s="2" t="n">
+      <c r="D56" s="3" t="n">
         <v>3.55355</v>
       </c>
       <c r="E56" t="inlineStr">
@@ -2345,13 +2346,13 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="F56" s="3" t="n">
         <v>4.059499117229809</v>
       </c>
-      <c r="G56" s="3" t="n">
+      <c r="G56" s="4" t="n">
         <v>14.12833709654593</v>
       </c>
-      <c r="H56" s="4" t="n">
+      <c r="H56" s="5" t="n">
         <v>2811.522128208124</v>
       </c>
     </row>
@@ -2361,9 +2362,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>002552.XSHE</t>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>002552</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2371,7 +2372,7 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="D57" s="3" t="n">
         <v>54.68463</v>
       </c>
       <c r="E57" t="inlineStr">
@@ -2379,13 +2380,13 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="F57" s="3" t="n">
         <v>59.10752117235049</v>
       </c>
-      <c r="G57" s="3" t="n">
+      <c r="G57" s="4" t="n">
         <v>7.970916429203726</v>
       </c>
-      <c r="H57" s="4" t="n">
+      <c r="H57" s="5" t="n">
         <v>1307.659847075781</v>
       </c>
     </row>
@@ -2395,9 +2396,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>301080.XSHE</t>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>301080</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2405,7 +2406,7 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="D58" s="2" t="n">
+      <c r="D58" s="3" t="n">
         <v>79.9799</v>
       </c>
       <c r="E58" t="inlineStr">
@@ -2413,13 +2414,13 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="F58" s="2" t="n">
+      <c r="F58" s="3" t="n">
         <v>88.12577138271428</v>
       </c>
-      <c r="G58" s="3" t="n">
+      <c r="G58" s="4" t="n">
         <v>10.06518817891633</v>
       </c>
-      <c r="H58" s="4" t="n">
+      <c r="H58" s="5" t="n">
         <v>1610.02548806182</v>
       </c>
     </row>
@@ -2429,9 +2430,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>600721.XSHG</t>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>600721</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2439,7 +2440,7 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n">
+      <c r="D59" s="3" t="n">
         <v>13.62361</v>
       </c>
       <c r="E59" t="inlineStr">
@@ -2447,13 +2448,13 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="F59" s="3" t="n">
         <v>13.8260749017484</v>
       </c>
-      <c r="G59" s="3" t="n">
+      <c r="G59" s="4" t="n">
         <v>1.380944627052953</v>
       </c>
-      <c r="H59" s="4" t="n">
+      <c r="H59" s="5" t="n">
         <v>263.3883144279083</v>
       </c>
     </row>
@@ -2463,9 +2464,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>300404.XSHE</t>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>300404</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2473,7 +2474,7 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n">
+      <c r="D60" s="3" t="n">
         <v>16.82681</v>
       </c>
       <c r="E60" t="inlineStr">
@@ -2481,13 +2482,13 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="F60" s="2" t="n">
+      <c r="F60" s="3" t="n">
         <v>15.70142941962338</v>
       </c>
-      <c r="G60" s="5" t="n">
+      <c r="G60" s="6" t="n">
         <v>-6.790636410416115</v>
       </c>
-      <c r="H60" s="6" t="n">
+      <c r="H60" s="7" t="n">
         <v>-1256.912235228694</v>
       </c>
     </row>
@@ -2497,9 +2498,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>300862.XSHE</t>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>300862</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2507,7 +2508,7 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n">
+      <c r="D61" s="3" t="n">
         <v>55.86581</v>
       </c>
       <c r="E61" t="inlineStr">
@@ -2515,13 +2516,13 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="F61" s="3" t="n">
         <v>54.45669273787662</v>
       </c>
-      <c r="G61" s="5" t="n">
+      <c r="G61" s="6" t="n">
         <v>-2.632705346710327</v>
       </c>
-      <c r="H61" s="6" t="n">
+      <c r="H61" s="7" t="n">
         <v>-441.2346500559096</v>
       </c>
     </row>
@@ -2531,9 +2532,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>603626.XSHG</t>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>603626</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2541,7 +2542,7 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D62" s="3" t="n">
         <v>19.3193</v>
       </c>
       <c r="E62" t="inlineStr">
@@ -2549,13 +2550,13 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="F62" s="3" t="n">
         <v>19.51947754637634</v>
       </c>
-      <c r="G62" s="3" t="n">
+      <c r="G62" s="4" t="n">
         <v>0.931863058328678</v>
       </c>
-      <c r="H62" s="4" t="n">
+      <c r="H62" s="5" t="n">
         <v>180.0294198276923</v>
       </c>
     </row>
@@ -2565,9 +2566,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>000712.XSHE</t>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>000712</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2575,7 +2576,7 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n">
+      <c r="D63" s="3" t="n">
         <v>13.32331</v>
       </c>
       <c r="E63" t="inlineStr">
@@ -2583,13 +2584,13 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="F63" s="3" t="n">
         <v>13.09776755848531</v>
       </c>
-      <c r="G63" s="5" t="n">
+      <c r="G63" s="6" t="n">
         <v>-1.794015171426532</v>
       </c>
-      <c r="H63" s="6" t="n">
+      <c r="H63" s="7" t="n">
         <v>-358.5333041042825</v>
       </c>
     </row>
@@ -2599,9 +2600,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>600722.XSHG</t>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>600722</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2609,7 +2610,7 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D64" s="3" t="n">
         <v>18.58857</v>
       </c>
       <c r="E64" t="inlineStr">
@@ -2617,13 +2618,13 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="F64" s="3" t="n">
         <v>17.91784531168013</v>
       </c>
-      <c r="G64" s="5" t="n">
+      <c r="G64" s="6" t="n">
         <v>-3.712220332864899</v>
       </c>
-      <c r="H64" s="6" t="n">
+      <c r="H64" s="7" t="n">
         <v>-690.0486751288246</v>
       </c>
     </row>
@@ -2633,9 +2634,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>600354.XSHG</t>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>600354</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2643,7 +2644,7 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D65" s="2" t="n">
+      <c r="D65" s="3" t="n">
         <v>10.82081</v>
       </c>
       <c r="E65" t="inlineStr">
@@ -2651,13 +2652,13 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="F65" s="3" t="n">
         <v>11.26312054420536</v>
       </c>
-      <c r="G65" s="3" t="n">
+      <c r="G65" s="4" t="n">
         <v>3.982165744267392</v>
       </c>
-      <c r="H65" s="4" t="n">
+      <c r="H65" s="5" t="n">
         <v>775.6246603300687</v>
       </c>
     </row>
@@ -2667,9 +2668,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>000993.XSHE</t>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>000993</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2677,7 +2678,7 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n">
+      <c r="D66" s="3" t="n">
         <v>18.3183</v>
       </c>
       <c r="E66" t="inlineStr">
@@ -2685,13 +2686,13 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="F66" s="3" t="n">
         <v>20.09822071496857</v>
       </c>
-      <c r="G66" s="3" t="n">
+      <c r="G66" s="4" t="n">
         <v>9.605080380842884</v>
       </c>
-      <c r="H66" s="4" t="n">
+      <c r="H66" s="5" t="n">
         <v>1759.487439403941</v>
       </c>
     </row>
@@ -2701,9 +2702,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>000002.XSHE</t>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>000002</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2711,7 +2712,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n">
+      <c r="D67" s="3" t="n">
         <v>3.81381</v>
       </c>
       <c r="E67" t="inlineStr">
@@ -2719,13 +2720,13 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="F67" s="2" t="n">
+      <c r="F67" s="3" t="n">
         <v>3.762110825397015</v>
       </c>
-      <c r="G67" s="5" t="n">
+      <c r="G67" s="6" t="n">
         <v>-1.457310829512077</v>
       </c>
-      <c r="H67" s="6" t="n">
+      <c r="H67" s="7" t="n">
         <v>-289.0111439644757</v>
       </c>
     </row>
@@ -2735,9 +2736,9 @@
           <t>策略一：连板断板承接</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>002119.XSHE</t>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>002119</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2745,7 +2746,7 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n">
+      <c r="D68" s="3" t="n">
         <v>29.09907</v>
       </c>
       <c r="E68" t="inlineStr">
@@ -2753,13 +2754,13 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="F68" s="2" t="n">
+      <c r="F68" s="3" t="n">
         <v>26.35944406543086</v>
       </c>
-      <c r="G68" s="5" t="n">
+      <c r="G68" s="6" t="n">
         <v>-9.519297037359513</v>
       </c>
-      <c r="H68" s="6" t="n">
+      <c r="H68" s="7" t="n">
         <v>-1662.016145045502</v>
       </c>
     </row>
